--- a/role_hours_daily.xlsx
+++ b/role_hours_daily.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,7 +1573,7 @@
         <v>137257</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>116063</v>
       </c>
     </row>
     <row r="33">
@@ -2031,11 +2031,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8am – 4pm</t>
+          <t>8am – 5pm</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G45" t="n">
         <v>137809</v>
@@ -2113,7 +2113,7 @@
         <v>137827</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>116093</v>
       </c>
     </row>
     <row r="48">
@@ -2499,11 +2499,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>8am – 6pm</t>
+          <t>8am – 7pm</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G58" t="n">
         <v>137970</v>
@@ -2571,11 +2571,11 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>8am – 5pm</t>
+          <t>8am – 5:30pm</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G60" t="n">
         <v>138005</v>
@@ -2643,11 +2643,11 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8am – 4pm</t>
+          <t>8am – 6pm</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G62" t="n">
         <v>138069</v>
@@ -2725,7 +2725,7 @@
         <v>138083</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>116075</v>
       </c>
     </row>
     <row r="65">
@@ -2797,7 +2797,7 @@
         <v>138118</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>116105</v>
       </c>
     </row>
     <row r="67">
@@ -2823,11 +2823,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>8am – 5pm</t>
+          <t>8am – 6pm</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G67" t="n">
         <v>138166</v>
@@ -2869,7 +2869,7 @@
         <v>138172</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>116159</v>
       </c>
     </row>
     <row r="69">
@@ -2952,32 +2952,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bay Ridge</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PCC Trainee</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Baran Düzgün</t>
+          <t>Ashley Peralta</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>8:30am – 6:30pm</t>
+          <t>8am – 4pm</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>138038</v>
+        <v>138203</v>
       </c>
       <c r="H71" t="n">
-        <v>116110</v>
+        <v>116320</v>
       </c>
     </row>
     <row r="72">
@@ -2988,32 +2988,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Upper East Side</t>
+          <t>Bay Ridge</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Avyanna Ojeda</t>
+          <t>Baran Düzgün</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>8:45am – 7pm</t>
+          <t>8:30am – 6:30pm</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="G72" t="n">
-        <v>137465</v>
+        <v>138038</v>
       </c>
       <c r="H72" t="n">
-        <v>116111</v>
+        <v>116110</v>
       </c>
     </row>
     <row r="73">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Astoria</t>
+          <t>Upper East Side</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Saidah Best</t>
+          <t>Avyanna Ojeda</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3046,10 +3046,10 @@
         <v>10.25</v>
       </c>
       <c r="G73" t="n">
-        <v>137473</v>
+        <v>137465</v>
       </c>
       <c r="H73" t="n">
-        <v>116107</v>
+        <v>116111</v>
       </c>
     </row>
     <row r="74">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hell's Kitchen</t>
+          <t>Astoria</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>JANELY CASTILLO</t>
+          <t>Saidah Best</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3082,10 +3082,10 @@
         <v>10.25</v>
       </c>
       <c r="G74" t="n">
-        <v>137553</v>
+        <v>137473</v>
       </c>
       <c r="H74" t="n">
-        <v>116126</v>
+        <v>116107</v>
       </c>
     </row>
     <row r="75">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Church Ave</t>
+          <t>Hell's Kitchen</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Rayana Jones</t>
+          <t>JANELY CASTILLO</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3118,10 +3118,10 @@
         <v>10.25</v>
       </c>
       <c r="G75" t="n">
-        <v>137641</v>
+        <v>137553</v>
       </c>
       <c r="H75" t="n">
-        <v>116133</v>
+        <v>116126</v>
       </c>
     </row>
     <row r="76">
@@ -3132,32 +3132,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Upper East Side</t>
+          <t>Church Ave</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Rowan Badran</t>
+          <t>Rayana Jones</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>9am – 7pm</t>
+          <t>8:45am – 7pm</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="G76" t="n">
-        <v>137278</v>
+        <v>137641</v>
       </c>
       <c r="H76" t="n">
-        <v>116128</v>
+        <v>116133</v>
       </c>
     </row>
     <row r="77">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Astoria</t>
+          <t>Upper East Side</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ammar Taha</t>
+          <t>Rowan Badran</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3190,10 +3190,10 @@
         <v>10</v>
       </c>
       <c r="G77" t="n">
-        <v>137340</v>
+        <v>137278</v>
       </c>
       <c r="H77" t="n">
-        <v>116124</v>
+        <v>116128</v>
       </c>
     </row>
     <row r="78">
@@ -3204,32 +3204,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Allerton</t>
+          <t>Astoria</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Zehra Syeda</t>
+          <t>Ammar Taha</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>9am – 6pm</t>
+          <t>9am – 7pm</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G78" t="n">
-        <v>137673</v>
+        <v>137340</v>
       </c>
       <c r="H78" t="n">
-        <v>116129</v>
+        <v>116124</v>
       </c>
     </row>
     <row r="79">
@@ -3240,32 +3240,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hell's Kitchen</t>
+          <t>Allerton</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Moustafa Mahmoud</t>
+          <t>Zehra Syeda</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>9am – 7pm</t>
+          <t>9am – 6pm</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G79" t="n">
-        <v>137749</v>
+        <v>137673</v>
       </c>
       <c r="H79" t="n">
-        <v>116132</v>
+        <v>116129</v>
       </c>
     </row>
     <row r="80">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HuntsPoint</t>
+          <t>Hell's Kitchen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Farrukh Jamil</t>
+          <t>Moustafa Mahmoud</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3298,10 +3298,10 @@
         <v>10</v>
       </c>
       <c r="G80" t="n">
-        <v>137803</v>
+        <v>137749</v>
       </c>
       <c r="H80" t="n">
-        <v>116130</v>
+        <v>116132</v>
       </c>
     </row>
     <row r="81">
@@ -3312,32 +3312,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bensonhurst  Pediatric</t>
+          <t>HuntsPoint</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Elena Argoudelis</t>
+          <t>Farrukh Jamil</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>9am – 5pm</t>
+          <t>9am – 7pm</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G81" t="n">
-        <v>137927</v>
+        <v>137803</v>
       </c>
       <c r="H81" t="n">
-        <v>116118</v>
+        <v>116130</v>
       </c>
     </row>
     <row r="82">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Site Coordinator</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Eva Zaghari</t>
+          <t>Elena Argoudelis</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3370,10 +3370,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>137931</v>
+        <v>137927</v>
       </c>
       <c r="H82" t="n">
-        <v>116120</v>
+        <v>116118</v>
       </c>
     </row>
     <row r="83">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Site Coordinator</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Barbara (Vanna) Tsilerides</t>
+          <t>Eva Zaghari</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3406,10 +3406,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>137935</v>
+        <v>137931</v>
       </c>
       <c r="H83" t="n">
-        <v>116136</v>
+        <v>116120</v>
       </c>
     </row>
     <row r="84">
@@ -3420,17 +3420,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Inwood</t>
+          <t>Bensonhurst  Pediatric</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Chaihinez Tahar</t>
+          <t>Barbara (Vanna) Tsilerides</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3442,10 +3442,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>137989</v>
+        <v>137935</v>
       </c>
       <c r="H84" t="n">
-        <v>116131</v>
+        <v>116136</v>
       </c>
     </row>
     <row r="85">
@@ -3456,32 +3456,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bedstuy</t>
+          <t>Inwood</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Iqra Hamid</t>
+          <t>Chaihinez Tahar</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>9am – 6pm</t>
+          <t>9am – 7pm</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G85" t="n">
-        <v>138094</v>
+        <v>137989</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>116131</v>
       </c>
     </row>
     <row r="86">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Church Ave</t>
+          <t>Bedstuy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3502,22 +3502,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mohammed Abdelaziz</t>
+          <t>Iqra Hamid</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>9am – 4pm</t>
+          <t>9am – 5pm</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>138121</v>
+        <v>138094</v>
       </c>
       <c r="H86" t="n">
-        <v>116123</v>
+        <v>116122</v>
       </c>
     </row>
     <row r="87">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sheepshead Bay</t>
+          <t>Church Ave</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3538,22 +3538,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Shehab Aser</t>
+          <t>Mohammed Abdelaziz</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>9am – 7pm</t>
+          <t>9am – 4:30pm</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G87" t="n">
-        <v>138131</v>
+        <v>138121</v>
       </c>
       <c r="H87" t="n">
-        <v>116115</v>
+        <v>116123</v>
       </c>
     </row>
     <row r="88">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sunset Park</t>
+          <t>Sheepshead Bay</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ruchi</t>
+          <t>Shehab Aser</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3586,10 +3586,10 @@
         <v>10</v>
       </c>
       <c r="G88" t="n">
-        <v>138134</v>
+        <v>138131</v>
       </c>
       <c r="H88" t="n">
-        <v>116116</v>
+        <v>116115</v>
       </c>
     </row>
     <row r="89">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Upper East Side</t>
+          <t>Sunset Park</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3610,22 +3610,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Vishal Bhartiya</t>
+          <t>Ruchi</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>9am – 2pm</t>
+          <t>9am – 7pm</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G89" t="n">
-        <v>138174</v>
+        <v>138134</v>
       </c>
       <c r="H89" t="n">
-        <v>116140</v>
+        <v>116116</v>
       </c>
     </row>
     <row r="90">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Allerton</t>
+          <t>Upper East Side</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Justin Feliciano</t>
+          <t>Vishal Bhartiya</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9:30am – 4pm</t>
+          <t>9am – 2pm</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>137675</v>
+        <v>138174</v>
       </c>
       <c r="H90" t="n">
-        <v>116138</v>
+        <v>116140</v>
       </c>
     </row>
     <row r="91">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Allerton</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3682,22 +3682,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ziah John</t>
+          <t>Justin Feliciano</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>9:45am – 7pm</t>
+          <t>9:30am – 4pm</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>9.25</v>
+        <v>6.5</v>
       </c>
       <c r="G91" t="n">
-        <v>137490</v>
+        <v>137675</v>
       </c>
       <c r="H91" t="n">
-        <v>116143</v>
+        <v>116138</v>
       </c>
     </row>
     <row r="92">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Grand Concourse</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Katelyn Ortiz</t>
+          <t>Ziah John</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3730,10 +3730,10 @@
         <v>9.25</v>
       </c>
       <c r="G92" t="n">
-        <v>137519</v>
+        <v>137490</v>
       </c>
       <c r="H92" t="n">
-        <v>116149</v>
+        <v>116143</v>
       </c>
     </row>
     <row r="93">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Greenpoint</t>
+          <t>Grand Concourse</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Taisha Gumbs</t>
+          <t>Katelyn Ortiz</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3766,10 +3766,10 @@
         <v>9.25</v>
       </c>
       <c r="G93" t="n">
-        <v>137644</v>
+        <v>137519</v>
       </c>
       <c r="H93" t="n">
-        <v>116151</v>
+        <v>116149</v>
       </c>
     </row>
     <row r="94">
@@ -3780,32 +3780,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Greenpoint</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Neha Solanki</t>
+          <t>Taisha Gumbs</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>10am – 7pm</t>
+          <t>9:45am – 7pm</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="G94" t="n">
-        <v>137245</v>
+        <v>137644</v>
       </c>
       <c r="H94" t="n">
-        <v>116142</v>
+        <v>116151</v>
       </c>
     </row>
     <row r="95">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Greenpoint</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Janviben Parmer</t>
+          <t>Neha Solanki</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3838,10 +3838,10 @@
         <v>9</v>
       </c>
       <c r="G95" t="n">
-        <v>137741</v>
+        <v>137245</v>
       </c>
       <c r="H95" t="n">
-        <v>116152</v>
+        <v>116142</v>
       </c>
     </row>
     <row r="96">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Grand Concourse</t>
+          <t>Greenpoint</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>RAMY ELKOUMY</t>
+          <t>Janviben Parmer</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3874,10 +3874,10 @@
         <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>137839</v>
+        <v>137741</v>
       </c>
       <c r="H96" t="n">
-        <v>116139</v>
+        <v>116152</v>
       </c>
     </row>
     <row r="97">
@@ -3893,27 +3893,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Surya Phani Gopagoni</t>
+          <t>RAMY ELKOUMY</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10am – 6pm</t>
+          <t>10am – 7pm</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G97" t="n">
-        <v>137844</v>
+        <v>137839</v>
       </c>
       <c r="H97" t="n">
-        <v>116146</v>
+        <v>116139</v>
       </c>
     </row>
     <row r="98">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Grand Concourse</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3934,22 +3934,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Khushboo Nadeem</t>
+          <t>Surya Phani Gopagoni</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>10am – 6pm</t>
+          <t>10am – 5pm</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G98" t="n">
-        <v>137960</v>
+        <v>137844</v>
       </c>
       <c r="H98" t="n">
-        <v>116144</v>
+        <v>116146</v>
       </c>
     </row>
     <row r="99">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Midwood</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Vidhi Padshala</t>
+          <t>Khushboo Nadeem</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3982,10 +3982,10 @@
         <v>8</v>
       </c>
       <c r="G99" t="n">
-        <v>138099</v>
+        <v>137960</v>
       </c>
       <c r="H99" t="n">
-        <v>116147</v>
+        <v>116144</v>
       </c>
     </row>
     <row r="100">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Church Ave</t>
+          <t>Midwood</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Nainika kiran reddy Bethi</t>
+          <t>Vidhi Padshala</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>10:30am – 2pm</t>
+          <t>10am – 6pm</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="G100" t="n">
-        <v>137885</v>
+        <v>138099</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>116147</v>
       </c>
     </row>
     <row r="101">
@@ -4032,32 +4032,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Church Ave</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Dhruvi Moradiya</t>
+          <t>Nainika kiran reddy Bethi</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>11am – 6:30pm</t>
+          <t>10:30am – 2pm</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="G101" t="n">
-        <v>137241</v>
+        <v>137885</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>116154</v>
       </c>
     </row>
     <row r="102">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sugar Hill</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4078,22 +4078,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Hamza Farooq</t>
+          <t>Dhruvi Moradiya</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>11am – 6pm</t>
+          <t>11am – 6:30pm</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G102" t="n">
-        <v>137892</v>
+        <v>137241</v>
       </c>
       <c r="H102" t="n">
-        <v>116157</v>
+        <v>116155</v>
       </c>
     </row>
     <row r="103">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bedstuy</t>
+          <t>Sugar Hill</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4114,22 +4114,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Dhruvi Nitinbhai Patel</t>
+          <t>Hamza Farooq</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>11am – 7pm</t>
+          <t>11am – 6pm</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G103" t="n">
-        <v>138055</v>
+        <v>137892</v>
       </c>
       <c r="H103" t="n">
-        <v>116156</v>
+        <v>116157</v>
       </c>
     </row>
     <row r="104">
@@ -4140,32 +4140,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Inwood</t>
+          <t>Bedstuy</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>WALEIDY HERRERA</t>
+          <t>Dhruvi Nitinbhai Patel</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>12pm – 7pm</t>
+          <t>11am – 7pm</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G104" t="n">
-        <v>137449</v>
+        <v>138055</v>
       </c>
       <c r="H104" t="n">
-        <v>116160</v>
+        <v>116156</v>
       </c>
     </row>
     <row r="105">
@@ -4176,17 +4176,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cobble Hill</t>
+          <t>Inwood</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Urvi Devmurari</t>
+          <t>WALEIDY HERRERA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4198,10 +4198,10 @@
         <v>7</v>
       </c>
       <c r="G105" t="n">
-        <v>137866</v>
+        <v>137449</v>
       </c>
       <c r="H105" t="n">
-        <v>116158</v>
+        <v>116160</v>
       </c>
     </row>
     <row r="106">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bensonhurst</t>
+          <t>Cobble Hill</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Megha Joshi</t>
+          <t>Urvi Devmurari</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4234,10 +4234,10 @@
         <v>7</v>
       </c>
       <c r="G106" t="n">
-        <v>138081</v>
+        <v>137866</v>
       </c>
       <c r="H106" t="n">
-        <v>116163</v>
+        <v>116158</v>
       </c>
     </row>
     <row r="107">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>Bensonhurst</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Jane Parmer</t>
+          <t>Megha Joshi</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4270,10 +4270,10 @@
         <v>7</v>
       </c>
       <c r="G107" t="n">
-        <v>138173</v>
+        <v>138081</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>116163</v>
       </c>
     </row>
     <row r="108">
@@ -4284,32 +4284,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Allerton</t>
+          <t>Midtown</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sajjad Ali</t>
+          <t>Jane Parmer</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1pm – 7pm</t>
+          <t>12pm – 7pm</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G108" t="n">
-        <v>137330</v>
+        <v>138173</v>
       </c>
       <c r="H108" t="n">
-        <v>116166</v>
+        <v>116161</v>
       </c>
     </row>
     <row r="109">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bushwick</t>
+          <t>Allerton</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DENISE DELEON</t>
+          <t>Sajjad Ali</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4342,10 +4342,10 @@
         <v>6</v>
       </c>
       <c r="G109" t="n">
-        <v>137455</v>
+        <v>137330</v>
       </c>
       <c r="H109" t="n">
-        <v>116169</v>
+        <v>116166</v>
       </c>
     </row>
     <row r="110">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Allerton</t>
+          <t>Bushwick</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Claire Jimenez Ramos</t>
+          <t>DENISE DELEON</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4378,10 +4378,10 @@
         <v>6</v>
       </c>
       <c r="G110" t="n">
-        <v>137618</v>
+        <v>137455</v>
       </c>
       <c r="H110" t="n">
-        <v>116168</v>
+        <v>116169</v>
       </c>
     </row>
     <row r="111">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Allerton</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4402,22 +4402,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Jammie Gamble</t>
+          <t>Claire Jimenez Ramos</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1pm – 6pm</t>
+          <t>1pm – 7pm</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G111" t="n">
-        <v>137654</v>
+        <v>137618</v>
       </c>
       <c r="H111" t="n">
-        <v>116165</v>
+        <v>116168</v>
       </c>
     </row>
     <row r="112">
@@ -4428,32 +4428,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tribeca</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Parth Thakkar</t>
+          <t>Jammie Gamble</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1pm – 8pm</t>
+          <t>1pm – 6pm</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G112" t="n">
-        <v>137760</v>
+        <v>137654</v>
       </c>
       <c r="H112" t="n">
-        <v>116164</v>
+        <v>116165</v>
       </c>
     </row>
     <row r="113">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Lenox Hill</t>
+          <t>Tribeca</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Shaineetha Bandari</t>
+          <t>Parth Thakkar</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4486,10 +4486,10 @@
         <v>7</v>
       </c>
       <c r="G113" t="n">
-        <v>137771</v>
+        <v>137760</v>
       </c>
       <c r="H113" t="n">
-        <v>116167</v>
+        <v>116164</v>
       </c>
     </row>
     <row r="114">
@@ -4500,32 +4500,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tribeca</t>
+          <t>Lenox Hill</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Vishal Bhartiya</t>
+          <t>Shaineetha Bandari</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2pm – 7pm</t>
+          <t>1pm – 8pm</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G114" t="n">
-        <v>137272</v>
+        <v>137771</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>116167</v>
       </c>
     </row>
     <row r="115">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PCC</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tara M Clarke</t>
+          <t>Vishal Bhartiya</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2pm – 8pm</t>
+          <t>2pm – 7pm</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G115" t="n">
-        <v>137552</v>
+        <v>137272</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>116177</v>
       </c>
     </row>
     <row r="116">
@@ -4572,32 +4572,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Clinton Hill</t>
+          <t>Tribeca</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCC</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Radhika Chavda</t>
+          <t>Tara M Clarke</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2pm – 7pm</t>
+          <t>2pm – 8pm</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G116" t="n">
-        <v>137871</v>
+        <v>137552</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>116171</v>
       </c>
     </row>
     <row r="117">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Church Ave</t>
+          <t>Clinton Hill</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Chibuzo Ezenwugo</t>
+          <t>Radhika Chavda</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4630,10 +4630,10 @@
         <v>5</v>
       </c>
       <c r="G117" t="n">
-        <v>137883</v>
+        <v>137871</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>116172</v>
       </c>
     </row>
     <row r="118">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Clinton Hill</t>
+          <t>Church Ave</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mahnoor Khursheed</t>
+          <t>Chibuzo Ezenwugo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4666,10 +4666,10 @@
         <v>5</v>
       </c>
       <c r="G118" t="n">
-        <v>138126</v>
+        <v>137883</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>116170</v>
       </c>
     </row>
     <row r="119">
@@ -4680,32 +4680,68 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>Clinton Hill</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PTA</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Mahnoor Khursheed</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2pm – 7pm</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>138126</v>
+      </c>
+      <c r="H119" t="n">
+        <v>116173</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>Midwood</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>Nainika kiran reddy Bethi</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>2:30pm – 7pm</t>
         </is>
       </c>
-      <c r="F119" t="n">
+      <c r="F120" t="n">
         <v>4.5</v>
       </c>
-      <c r="G119" t="n">
+      <c r="G120" t="n">
         <v>137825</v>
       </c>
-      <c r="H119" t="n">
-        <v>0</v>
+      <c r="H120" t="n">
+        <v>116174</v>
       </c>
     </row>
   </sheetData>
@@ -4719,7 +4755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5041,7 +5077,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20.25</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="17">
@@ -5161,7 +5197,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19.25</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="23">
@@ -5372,16 +5408,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PCC Trainee</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Allerton</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -5397,11 +5433,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Astoria</t>
+          <t>Allerton</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -5417,11 +5453,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bay Ridge</t>
+          <t>Astoria</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -5437,11 +5473,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bedstuy</t>
+          <t>Bay Ridge</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -5457,11 +5493,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bensonhurst</t>
+          <t>Bedstuy</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -5477,11 +5513,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bensonhurst  Pediatric</t>
+          <t>Bensonhurst</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -5497,11 +5533,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brownsville</t>
+          <t>Bensonhurst  Pediatric</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -5517,7 +5553,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bushwick</t>
+          <t>Brownsville</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -5537,7 +5573,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Castle Hill</t>
+          <t>Bushwick</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -5557,7 +5593,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Central Harlem</t>
+          <t>Castle Hill</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5577,11 +5613,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Central Harlem</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
@@ -5597,11 +5633,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Church Ave</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -5617,11 +5653,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Clinton Hill</t>
+          <t>Church Ave</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="46">
@@ -5637,7 +5673,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cobble Hill</t>
+          <t>Clinton Hill</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5657,7 +5693,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Corona</t>
+          <t>Cobble Hill</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -5677,7 +5713,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Flatbush</t>
+          <t>Corona</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -5697,7 +5733,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>Flatbush</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5717,11 +5753,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Grand Concourse</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
@@ -5737,7 +5773,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greenpoint</t>
+          <t>Grand Concourse</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -5757,11 +5793,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hell's Kitchen</t>
+          <t>Greenpoint</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
@@ -5777,11 +5813,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HuntsPoint</t>
+          <t>Hell's Kitchen</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
@@ -5797,11 +5833,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Inwood</t>
+          <t>HuntsPoint</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -5817,7 +5853,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Inwood</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -5837,11 +5873,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lenox Hill</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -5857,7 +5893,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Midtown</t>
+          <t>Lenox Hill</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -5877,11 +5913,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Midwood</t>
+          <t>Midtown</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -5897,11 +5933,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Midwood</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -5917,11 +5953,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sheepshead Bay</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -5937,11 +5973,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sugar Hill</t>
+          <t>Sheepshead Bay</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">
@@ -5957,11 +5993,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunset Park</t>
+          <t>Sugar Hill</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -5977,11 +6013,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tribeca</t>
+          <t>Sunset Park</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
@@ -5997,11 +6033,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Upper East Side</t>
+          <t>Tribeca</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -6012,16 +6048,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PTA</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Allerton</t>
+          <t>Upper East Side</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -6037,11 +6073,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bay Ridge</t>
+          <t>Allerton</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -6057,11 +6093,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bedstuy</t>
+          <t>Bay Ridge</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
@@ -6077,11 +6113,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bensonhurst</t>
+          <t>Bedstuy</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
@@ -6097,11 +6133,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brownsville</t>
+          <t>Bensonhurst</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -6117,7 +6153,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bushwick</t>
+          <t>Brownsville</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -6137,11 +6173,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Castle Hill</t>
+          <t>Bushwick</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
@@ -6157,11 +6193,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Central Harlem</t>
+          <t>Castle Hill</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="73">
@@ -6177,11 +6213,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Central Harlem</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
@@ -6197,11 +6233,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Church Ave</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="75">
@@ -6217,11 +6253,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Clinton Hill</t>
+          <t>Church Ave</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="76">
@@ -6237,11 +6273,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Corona</t>
+          <t>Clinton Hill</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -6257,7 +6293,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Flatbush</t>
+          <t>Corona</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -6277,11 +6313,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>Flatbush</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -6297,11 +6333,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Grand Concourse</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
@@ -6317,11 +6353,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HuntsPoint</t>
+          <t>Grand Concourse</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -6337,11 +6373,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inwood</t>
+          <t>HuntsPoint</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
@@ -6357,11 +6393,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Inwood</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
@@ -6377,11 +6413,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Midwood</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
@@ -6397,7 +6433,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Midwood</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -6417,11 +6453,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sheepshead Bay</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86">
@@ -6437,11 +6473,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sugar Hill</t>
+          <t>Sheepshead Bay</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -6457,11 +6493,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunset Park</t>
+          <t>Sugar Hill</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -6477,11 +6513,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tribeca</t>
+          <t>Sunset Park</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -6497,7 +6533,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Upper East Side</t>
+          <t>Tribeca</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -6512,16 +6548,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Service Coordinator</t>
+          <t>PTA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bensonhurst  Pediatric</t>
+          <t>Upper East Side</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -6532,15 +6568,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>Service Coordinator</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Bensonhurst  Pediatric</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>Site Coordinator</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Bensonhurst  Pediatric</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D92" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6555,7 +6611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6576,20 +6632,25 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>PCC Trainee</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PTA</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Service Coordinator</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Site Coordinator</t>
         </is>
@@ -6610,15 +6671,18 @@
         <v>17.75</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>12</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>9</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6637,15 +6701,18 @@
         <v>10.25</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6664,15 +6731,18 @@
         <v>17.25</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>11</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6691,15 +6761,18 @@
         <v>13.25</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>13</v>
       </c>
-      <c r="E5" t="n">
-        <v>24</v>
-      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6718,15 +6791,18 @@
         <v>11.25</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>11</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>15</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6745,17 +6821,20 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>16</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>8</v>
       </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6772,15 +6851,18 @@
         <v>11.25</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>11</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>19</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6799,15 +6881,18 @@
         <v>11.25</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>11</v>
       </c>
-      <c r="E9" t="n">
-        <v>19</v>
-      </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6826,15 +6911,18 @@
         <v>18.25</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>11</v>
       </c>
-      <c r="E10" t="n">
-        <v>9</v>
-      </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6853,15 +6941,18 @@
         <v>11.25</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6880,15 +6971,18 @@
         <v>9.25</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>9</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>7.5</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6907,15 +7001,18 @@
         <v>10.25</v>
       </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>8.5</v>
       </c>
-      <c r="E13" t="n">
-        <v>7</v>
-      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6934,15 +7031,18 @@
         <v>11.25</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>11</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>5</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6961,15 +7061,18 @@
         <v>11.25</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
         <v>11</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6988,15 +7091,18 @@
         <v>16.75</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7012,18 +7118,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.25</v>
+        <v>21.25</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7042,15 +7151,18 @@
         <v>11.25</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>11</v>
       </c>
-      <c r="E18" t="n">
-        <v>10</v>
-      </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7069,15 +7181,18 @@
         <v>9.25</v>
       </c>
       <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
         <v>9</v>
       </c>
-      <c r="E19" t="n">
-        <v>8</v>
-      </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7096,15 +7211,18 @@
         <v>9.25</v>
       </c>
       <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
         <v>9</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7123,15 +7241,18 @@
         <v>10.25</v>
       </c>
       <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7150,15 +7271,18 @@
         <v>12.25</v>
       </c>
       <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
         <v>12</v>
       </c>
-      <c r="E22" t="n">
-        <v>18</v>
-      </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7174,18 +7298,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19.25</v>
+        <v>21.25</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7204,15 +7331,18 @@
         <v>11.25</v>
       </c>
       <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
         <v>11</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>22</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7231,15 +7361,18 @@
         <v>12.25</v>
       </c>
       <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>12</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7258,15 +7391,18 @@
         <v>19.25</v>
       </c>
       <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>12</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7285,15 +7421,18 @@
         <v>11.25</v>
       </c>
       <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
         <v>11</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>8</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7312,15 +7451,18 @@
         <v>10.25</v>
       </c>
       <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>8</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7339,15 +7481,18 @@
         <v>11.25</v>
       </c>
       <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
         <v>11</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>10</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7366,15 +7511,18 @@
         <v>20.25</v>
       </c>
       <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
         <v>10</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>7</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7393,15 +7541,18 @@
         <v>11.25</v>
       </c>
       <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>11</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>10</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7420,15 +7571,18 @@
         <v>12.25</v>
       </c>
       <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
         <v>12</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>5</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7447,15 +7601,18 @@
         <v>10.25</v>
       </c>
       <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
         <v>10</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>5</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
         <v>0</v>
       </c>
     </row>
